--- a/healthcare_forms/021_passenger_self_reporting_form--healthcare_forms.xlsx
+++ b/healthcare_forms/021_passenger_self_reporting_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Travel Agency</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your travel agency?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select your travel agency</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AirPort</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What airports did you travel from?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select all airports you visited</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,7 +579,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>Describe your symptoms</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -625,7 +633,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -652,7 +660,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travel Date</t>
+          <t>Travel date</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -675,7 +683,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travel Time</t>
+          <t>Travel time</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -698,7 +706,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Travel Location</t>
+          <t>Travel location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -744,7 +752,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Flight Number</t>
+          <t>Flight number</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -762,12 +770,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>flight_number2</t>
+          <t>travel_duration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Flight Number 2</t>
+          <t>Travel duration</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -780,320 +788,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>flight_number3</t>
+          <t>travel_agency_type</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Flight Number 3</t>
+          <t>Travel agency type</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>travel_type</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Travel Type</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>travel_duration</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Travel Duration</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>travel_agency</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Travel Agency</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>airport</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Airport</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>travel_time2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Travel Time 2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>travel_date2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Travel Date 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>travel_duration2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Travel Duration 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>airline</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Airline</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>travel_agency2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Travel Agency 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>airport2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Airport 2</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>flight_number</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Flight Number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>travel_time2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Travel Time 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>flight_number2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Flight Number 2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1110,12 +819,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +852,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'79034-1',_'label':_'abc_travels'}</t>
+          <t>abc_travels</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '79034-1', 'label': 'ABC Travels'}</t>
+          <t>ABC Travels</t>
         </is>
       </c>
     </row>
@@ -1160,12 +869,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'79034-2',_'label':_'def_travels'}</t>
+          <t>def_travels</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '79034-2', 'label': 'DEF Travels'}</t>
+          <t>DEF Travels</t>
         </is>
       </c>
     </row>
@@ -1177,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'79034-2',_'label':_'airport_1'}</t>
+          <t>airport_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '79034-2', 'label': 'Airport 1'}</t>
+          <t>Airport 1</t>
         </is>
       </c>
     </row>
@@ -1194,12 +903,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'79034-3',_'label':_'airport_2'}</t>
+          <t>airport_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '79034-3', 'label': 'Airport 2'}</t>
+          <t>Airport 2</t>
         </is>
       </c>
     </row>
@@ -1211,165 +920,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'79034-4',_'label':_'airport_3'}</t>
+          <t>airport_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '79034-4', 'label': 'Airport 3'}</t>
+          <t>Airport 3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>travel_agency_choices</t>
+          <t>travel_agency_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'79034-1',_'label':_'abc_travels'}</t>
+          <t>def_travels</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '79034-1', 'label': 'ABC Travels'}</t>
+          <t>DEF Travels</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>travel_agency_choices</t>
+          <t>travel_agency_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'79034-2',_'label':_'def_travels'}</t>
+          <t>ghi_travels</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '79034-2', 'label': 'DEF Travels'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>airport_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-2',_'label':_'airport_1'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': '79034-2', 'label': 'Airport 1'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>airport_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-3',_'label':_'airport_2'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': '79034-3', 'label': 'Airport 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>airport_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-4',_'label':_'airport_3'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': '79034-4', 'label': 'Airport 3'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>travel_agency2_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-2',_'label':_'def_travels'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': '79034-2', 'label': 'DEF Travels'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>travel_agency2_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-3',_'label':_'ghi_travels'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': '79034-3', 'label': 'GHI Travels'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>airport2_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-3',_'label':_'airport_2'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': '79034-3', 'label': 'Airport 2'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>airport2_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_'79034-4',_'label':_'airport_3'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': '79034-4', 'label': 'Airport 3'}</t>
+          <t>GHI Travels</t>
         </is>
       </c>
     </row>
